--- a/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$66</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2526" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2607" uniqueCount="532">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T14:57:23+00:00</t>
+    <t>2026-10-13T09:06:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1158,7 +1158,11 @@
     <t>Use of the Health Care Privacy/Security Classification (HCS) system of security-tag use is recommended.</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J08-XdsConfidentialityCode-CISIS/FHIR/JDV-J08-XdsConfidentialityCode-CISIS</t>
+    <t xml:space="preserve">value:$this}
+</t>
+  </si>
+  <si>
+    <t>Slice sur securityLabel pour distinguer le niveau de confidentialité (U, L, M, N, R, V) du statut de visibilité (MASQUE_PS, INVISIBLE_PATIENT, etc...) : chaque slice est discriminée par son required binding sur un ValueSet fermé (v3-ConfidentialityClassification pour confidentiality, JDV_J110-StatutVisibiliteDocument-CISIS pour visibilityStatus)</t>
   </si>
   <si>
     <t>Composition.confidentiality, Composition.meta.security</t>
@@ -1174,6 +1178,30 @@
   </si>
   <si>
     <t>DocumentEntry.confidentialityCode</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:confidentiality</t>
+  </si>
+  <si>
+    <t>confidentiality</t>
+  </si>
+  <si>
+    <t>Niveau de confidentialité standard du document (Normal, Restreint, Très restreint, ...). En l'absence d'information de confidentialité disponible, la valeur par défaut à utiliser est N (Normal), conformément à ce qui est déjà pratiqué aujourd'hui pour les documents CDA.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-Confidentiality</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:visibilityStatus</t>
+  </si>
+  <si>
+    <t>visibilityStatus</t>
+  </si>
+  <si>
+    <t>Statut de visibilité du document (invisible patient, invisible représentants légaux, masqué PS, etc...).</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J110-StatutVisibiliteDocument-CISIS/FHIR/JDV-J110-StatutVisibiliteDocument-CISIS</t>
   </si>
   <si>
     <t>DocumentReference.content</t>
@@ -1978,12 +2006,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ64"/>
+  <dimension ref="A1:AQ66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="43.578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.37890625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -2009,7 +2037,7 @@
     <col min="26" max="26" width="102.93359375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="255.0" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="37.78125" customWidth="true" bestFit="true" hidden="true"/>
@@ -6449,7 +6477,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>358</v>
       </c>
@@ -6462,7 +6490,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>82</v>
@@ -6516,24 +6544,26 @@
       <c r="X37" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="Y37" s="2"/>
+      <c r="Y37" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="Z37" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB37" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AA37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AC37" t="s" s="2">
-        <v>80</v>
+        <v>364</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>358</v>
@@ -6554,32 +6584,34 @@
         <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="D38" t="s" s="2">
         <v>80</v>
       </c>
@@ -6600,16 +6632,20 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>316</v>
+        <v>242</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
       </c>
@@ -6633,13 +6669,11 @@
         <v>80</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>80</v>
+        <v>373</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>80</v>
@@ -6657,10 +6691,10 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>82</v>
@@ -6675,32 +6709,34 @@
         <v>80</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>80</v>
+        <v>367</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>80</v>
+        <v>368</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>80</v>
+        <v>369</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>374</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="C39" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="D39" t="s" s="2">
         <v>80</v>
       </c>
@@ -6709,28 +6745,32 @@
         <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>107</v>
+        <v>242</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>108</v>
+        <v>376</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
       </c>
@@ -6754,13 +6794,11 @@
         <v>80</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>80</v>
+        <v>377</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>80</v>
@@ -6778,81 +6816,79 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>110</v>
+        <v>358</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>80</v>
+        <v>365</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>111</v>
+        <v>366</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>80</v>
+        <v>367</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>80</v>
+        <v>368</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>80</v>
+        <v>369</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>114</v>
+        <v>316</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>115</v>
+        <v>379</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>80</v>
@@ -6901,10 +6937,10 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>121</v>
+        <v>378</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>82</v>
@@ -6913,16 +6949,16 @@
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>80</v>
+        <v>381</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>111</v>
+        <v>382</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>80</v>
@@ -6939,46 +6975,42 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>327</v>
+        <v>80</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>328</v>
+        <v>108</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>80</v>
       </c>
@@ -7026,19 +7058,19 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>331</v>
+        <v>110</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>80</v>
@@ -7047,7 +7079,7 @@
         <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>192</v>
+        <v>111</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>80</v>
@@ -7064,21 +7096,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>80</v>
@@ -7087,18 +7119,20 @@
         <v>80</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>378</v>
+        <v>114</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>379</v>
+        <v>115</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -7147,40 +7181,40 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>377</v>
+        <v>121</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>381</v>
+        <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>373</v>
+        <v>111</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>382</v>
+        <v>80</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>383</v>
+        <v>80</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>384</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" hidden="true">
@@ -7192,35 +7226,39 @@
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>80</v>
+        <v>327</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>108</v>
+        <v>328</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
       </c>
@@ -7268,19 +7306,19 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>110</v>
+        <v>331</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>80</v>
@@ -7289,7 +7327,7 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>111</v>
+        <v>192</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>80</v>
@@ -7313,14 +7351,14 @@
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>80</v>
@@ -7329,20 +7367,18 @@
         <v>80</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>114</v>
+        <v>387</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>115</v>
+        <v>388</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>80</v>
@@ -7379,60 +7415,60 @@
         <v>80</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>121</v>
+        <v>386</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>80</v>
+        <v>390</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>111</v>
+        <v>382</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>80</v>
+        <v>391</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>80</v>
+        <v>392</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>80</v>
+        <v>393</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7440,7 +7476,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>93</v>
@@ -7452,21 +7488,19 @@
         <v>80</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>388</v>
+        <v>108</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>389</v>
+        <v>109</v>
       </c>
       <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>390</v>
-      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>80</v>
       </c>
@@ -7478,7 +7512,7 @@
         <v>80</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>391</v>
+        <v>80</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>80</v>
@@ -7490,13 +7524,13 @@
         <v>80</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>224</v>
+        <v>80</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>392</v>
+        <v>80</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>393</v>
+        <v>80</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>80</v>
@@ -7514,7 +7548,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>394</v>
+        <v>110</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7526,7 +7560,7 @@
         <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>80</v>
@@ -7535,61 +7569,61 @@
         <v>80</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ45" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="AN45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="AQ45" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="2">
-        <v>397</v>
-      </c>
       <c r="B46" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>169</v>
+        <v>114</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>398</v>
+        <v>115</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>400</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>80</v>
       </c>
@@ -7601,7 +7635,7 @@
         <v>80</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>401</v>
+        <v>80</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>80</v>
@@ -7613,43 +7647,43 @@
         <v>80</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>175</v>
+        <v>80</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>402</v>
+        <v>121</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>80</v>
@@ -7658,7 +7692,7 @@
         <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>403</v>
+        <v>111</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>80</v>
@@ -7675,10 +7709,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7698,22 +7732,20 @@
         <v>80</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>405</v>
+        <v>169</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>408</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -7726,7 +7758,7 @@
         <v>80</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>80</v>
@@ -7738,13 +7770,13 @@
         <v>80</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>80</v>
+        <v>224</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>80</v>
+        <v>401</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>80</v>
+        <v>402</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>80</v>
@@ -7762,7 +7794,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7783,7 +7815,7 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>80</v>
@@ -7792,18 +7824,18 @@
         <v>80</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7814,10 +7846,10 @@
         <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>80</v>
@@ -7826,19 +7858,17 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>414</v>
+        <v>169</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -7851,7 +7881,7 @@
         <v>80</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>80</v>
@@ -7863,13 +7893,13 @@
         <v>80</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>80</v>
+        <v>173</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>80</v>
@@ -7887,7 +7917,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7908,7 +7938,7 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>80</v>
@@ -7917,7 +7947,7 @@
         <v>80</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>422</v>
+        <v>80</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>80</v>
@@ -7925,10 +7955,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7936,7 +7966,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>93</v>
@@ -7948,22 +7978,22 @@
         <v>80</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -8012,7 +8042,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8033,7 +8063,7 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>80</v>
@@ -8042,7 +8072,7 @@
         <v>80</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>80</v>
+        <v>421</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>80</v>
@@ -8050,10 +8080,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8064,7 +8094,7 @@
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>80</v>
@@ -8076,19 +8106,19 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8101,7 +8131,7 @@
         <v>80</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>80</v>
+        <v>428</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>80</v>
@@ -8137,7 +8167,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8158,7 +8188,7 @@
         <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>80</v>
@@ -8167,7 +8197,7 @@
         <v>80</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>80</v>
+        <v>431</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>80</v>
@@ -8175,10 +8205,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8186,7 +8216,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>93</v>
@@ -8201,17 +8231,19 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>107</v>
+        <v>433</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="O51" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -8224,7 +8256,7 @@
         <v>80</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>442</v>
+        <v>80</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>80</v>
@@ -8260,7 +8292,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8281,7 +8313,7 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
@@ -8296,12 +8328,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8315,7 +8347,7 @@
         <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>80</v>
@@ -8324,17 +8356,19 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>446</v>
+        <v>414</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="O52" t="s" s="2">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8383,7 +8417,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8404,7 +8438,7 @@
         <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>80</v>
@@ -8419,12 +8453,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8432,13 +8466,13 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>80</v>
@@ -8447,18 +8481,18 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>449</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
       </c>
@@ -8470,7 +8504,7 @@
         <v>80</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>80</v>
+        <v>451</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>80</v>
@@ -8482,11 +8516,13 @@
         <v>80</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y53" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z53" t="s" s="2">
-        <v>455</v>
+        <v>80</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -8504,7 +8540,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8516,19 +8552,19 @@
         <v>80</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>456</v>
+        <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>457</v>
+        <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>373</v>
+        <v>453</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>458</v>
+        <v>80</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>80</v>
@@ -8537,15 +8573,15 @@
         <v>80</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>459</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8568,18 +8604,18 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>316</v>
+        <v>455</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>457</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>458</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
       </c>
@@ -8627,7 +8663,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8648,7 +8684,7 @@
         <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>464</v>
+        <v>439</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>80</v>
@@ -8663,12 +8699,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8682,24 +8718,26 @@
         <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>108</v>
+        <v>461</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -8724,13 +8762,11 @@
         <v>80</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>80</v>
+        <v>464</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>80</v>
@@ -8748,7 +8784,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>110</v>
+        <v>460</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8760,19 +8796,19 @@
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>80</v>
+        <v>465</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>80</v>
+        <v>466</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>111</v>
+        <v>382</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>80</v>
+        <v>467</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>80</v>
@@ -8781,47 +8817,47 @@
         <v>80</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>80</v>
+        <v>468</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>114</v>
+        <v>316</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>115</v>
+        <v>470</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>116</v>
+        <v>471</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>117</v>
+        <v>472</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8871,19 +8907,19 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>121</v>
+        <v>469</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>80</v>
@@ -8892,7 +8928,7 @@
         <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>111</v>
+        <v>473</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>80</v>
@@ -8909,46 +8945,42 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>327</v>
+        <v>80</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>328</v>
+        <v>108</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>80</v>
       </c>
@@ -8996,19 +9028,19 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>331</v>
+        <v>110</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>80</v>
@@ -9017,7 +9049,7 @@
         <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>192</v>
+        <v>111</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>80</v>
@@ -9034,14 +9066,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9060,15 +9092,17 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>469</v>
+        <v>114</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>470</v>
+        <v>115</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>80</v>
@@ -9117,7 +9151,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>468</v>
+        <v>121</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9129,22 +9163,22 @@
         <v>80</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>472</v>
+        <v>80</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>473</v>
+        <v>80</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>474</v>
+        <v>111</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>475</v>
+        <v>80</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>80</v>
@@ -9162,37 +9196,39 @@
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>80</v>
+        <v>327</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>242</v>
+        <v>114</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>477</v>
+        <v>328</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>478</v>
+        <v>329</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
       </c>
@@ -9216,13 +9252,13 @@
         <v>80</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>159</v>
+        <v>80</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>480</v>
+        <v>80</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>481</v>
+        <v>80</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -9240,7 +9276,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>476</v>
+        <v>331</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9252,16 +9288,16 @@
         <v>80</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>482</v>
+        <v>122</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>483</v>
+        <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>484</v>
+        <v>192</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>80</v>
@@ -9273,15 +9309,15 @@
         <v>80</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>485</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9292,25 +9328,25 @@
         <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9361,13 +9397,13 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>80</v>
@@ -9376,33 +9412,33 @@
         <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>80</v>
+        <v>481</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>492</v>
+        <v>80</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>80</v>
+        <v>484</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>493</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9416,7 +9452,7 @@
         <v>93</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>80</v>
@@ -9428,12 +9464,14 @@
         <v>242</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>487</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>488</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>80</v>
@@ -9458,11 +9496,13 @@
         <v>80</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y61" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="Z61" t="s" s="2">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>80</v>
@@ -9480,48 +9520,48 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ61" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ61" t="s" s="2">
-        <v>502</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9541,23 +9581,19 @@
         <v>80</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>242</v>
+        <v>496</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>507</v>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>80</v>
       </c>
@@ -9581,11 +9617,13 @@
         <v>80</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y62" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z62" t="s" s="2">
-        <v>508</v>
+        <v>80</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>80</v>
@@ -9603,7 +9641,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9615,7 +9653,7 @@
         <v>80</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>498</v>
+        <v>105</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>80</v>
@@ -9627,7 +9665,7 @@
         <v>500</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>80</v>
@@ -9636,15 +9674,15 @@
         <v>80</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>509</v>
+        <v>502</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9667,13 +9705,13 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>267</v>
+        <v>242</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9700,13 +9738,11 @@
         <v>80</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>80</v>
+        <v>506</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>80</v>
@@ -9724,7 +9760,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9736,19 +9772,19 @@
         <v>80</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>105</v>
+        <v>507</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>271</v>
+        <v>508</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>272</v>
+        <v>509</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>273</v>
+        <v>510</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>80</v>
@@ -9757,15 +9793,15 @@
         <v>80</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9776,10 +9812,10 @@
         <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>80</v>
@@ -9788,18 +9824,20 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="M64" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>80</v>
       </c>
@@ -9823,13 +9861,11 @@
         <v>80</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>80</v>
+        <v>517</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>80</v>
@@ -9847,44 +9883,288 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ64" t="s" s="2">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ65" t="s" s="2">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G66" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AI64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
+      <c r="H66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AK64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ64" t="s" s="2">
-        <v>522</v>
+      <c r="AK66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ66" t="s" s="2">
+        <v>531</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ64">
+  <autoFilter ref="A1:AQ66">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9894,7 +10174,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI63">
+  <conditionalFormatting sqref="A2:AI65">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
